--- a/XlsxSharp.Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -1,200 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Rich Text" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Rich Text" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">The </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FFFF0000"/>
-        <x:rFont val="Courier"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>show</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> must go on...</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>" BIG " is Bold.</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FFFF0000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>Hell</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:u val="single"/>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FFFF0000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>o</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:u val="single"/>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> BIG </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:u val="single"/>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FFFF0000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>W</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FFFF0000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>orld</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF008000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>Some</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> rich text </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>with a gray background</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="25"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-        <x:family val="2"/>
-        <x:scheme val="major"/>
-      </x:rPr>
-      <x:t>Major scheme</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="25"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="25"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Times New Roman"/>
-        <x:family val="2"/>
-        <x:scheme val="minor"/>
-      </x:rPr>
-      <x:t>Minor scheme</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="25"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="25"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Cambria"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>No scheme</x:t>
-    </x:r>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier"/>
+        <family val="2"/>
+      </rPr>
+      <t>show</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must go on...</t>
+    </r>
+  </si>
+  <si>
+    <t>" BIG " is Bold.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hell</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>o</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u val="single"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> BIG </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>orld</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Some</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> rich text </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>with a gray background</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="25"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Major scheme</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="25"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="25"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Minor scheme</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="25"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="25"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
+      </rPr>
+      <t>No scheme</t>
+    </r>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,48 +550,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:B6"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="88.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="35.282054" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:2">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2">
-      <x:c r="A3" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2">
-      <x:c r="A5" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:2">
-      <x:c r="A6" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="88.710625"/>
+    <col min="2" max="2" style="0" customWidth="1" width="35.282054"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>